--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:00:53+00:00</t>
+    <t>2023-06-02T12:29:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-number-arhgos</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-number-arhgos</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-number-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
